--- a/wasa-intervention-form.xlsx
+++ b/wasa-intervention-form.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{542D5B16-47D7-47D7-AE55-FE2BB63FB0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF8C21E5-5664-435E-91DE-69B7FB04696C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{5D5F3748-DAFD-4827-A51E-48132B110982}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{656C6799-462E-4A6D-BCC2-557CC4DD342B}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="87">
   <si>
     <t>type</t>
   </si>
@@ -148,21 +148,69 @@
     <t>Capture the GPS coordinates of this site</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>photos_note</t>
+  </si>
+  <si>
+    <t>## Photos (at least 3, must be geotagged)</t>
+  </si>
+  <si>
+    <t>Device location services MUST be enabled so EXIF GPS is written to each photo.</t>
+  </si>
+  <si>
     <t>image</t>
   </si>
   <si>
-    <t>photo</t>
-  </si>
-  <si>
-    <t>Photo of intervention (geotagged)</t>
-  </si>
-  <si>
-    <t>Take the photo with the device camera. Device location services MUST be enabled so EXIF GPS is written to the file.</t>
+    <t>photo_1</t>
+  </si>
+  <si>
+    <t>Photo 1 - Overview</t>
+  </si>
+  <si>
+    <t>Wide shot showing the whole site.</t>
   </si>
   <si>
     <t>max-pixels=2048</t>
   </si>
   <si>
+    <t>photo_2</t>
+  </si>
+  <si>
+    <t>Photo 2 - Detail</t>
+  </si>
+  <si>
+    <t>Close-up of the intervention itself.</t>
+  </si>
+  <si>
+    <t>photo_3</t>
+  </si>
+  <si>
+    <t>Photo 3 - Context</t>
+  </si>
+  <si>
+    <t>Showing the intervention in its surrounding landscape.</t>
+  </si>
+  <si>
+    <t>photo_4</t>
+  </si>
+  <si>
+    <t>Photo 4 (optional)</t>
+  </si>
+  <si>
+    <t>Extra photo - beneficiaries, before/after, signage, anything useful.</t>
+  </si>
+  <si>
+    <t>photo_5</t>
+  </si>
+  <si>
+    <t>Photo 5 (optional)</t>
+  </si>
+  <si>
+    <t>Extra photo.</t>
+  </si>
+  <si>
     <t>comment</t>
   </si>
   <si>
@@ -244,10 +292,10 @@
     <t>WASA Intervention Inventory</t>
   </si>
   <si>
-    <t>wasa_intervention_v1</t>
-  </si>
-  <si>
-    <t>2026.05.28</t>
+    <t>wasa_intervention_v2</t>
+  </si>
+  <si>
+    <t>2026.05.28.2</t>
   </si>
   <si>
     <t>en</t>
@@ -613,16 +661,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99385AB4-D32B-44B2-800E-794F45038E30}">
-  <dimension ref="A1:G12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D1AEA8-E490-4A79-BF69-B3584A8A2767}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="105.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="72.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -785,19 +833,13 @@
       <c r="C11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
       <c r="F11" t="s">
         <v>38</v>
       </c>
-      <c r="G11" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
@@ -806,13 +848,107 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" t="s">
         <v>42</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" t="s">
         <v>28</v>
       </c>
-      <c r="F12" t="s">
-        <v>43</v>
+      <c r="F17" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -821,7 +957,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3F5A960-5C60-4135-BCE4-BE818ED5FD5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBD1968-0C81-4C75-9DCC-6B68690BADFF}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -832,7 +968,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -846,10 +982,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -857,10 +993,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -868,10 +1004,10 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -879,10 +1015,10 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -890,10 +1026,10 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -901,10 +1037,10 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -912,10 +1048,10 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -923,10 +1059,10 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -935,49 +1071,49 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19E4D84E-C216-488F-9C7F-6898FD03A22D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5023EBA-5FD9-4A94-92A1-EE79071BBC46}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="71.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/wasa-intervention-form.xlsx
+++ b/wasa-intervention-form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF8C21E5-5664-435E-91DE-69B7FB04696C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F16ED20-C14F-485A-A608-C3705299E172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{656C6799-462E-4A6D-BCC2-557CC4DD342B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24EAA487-CC81-403E-BAAF-7584F6353F78}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
   <si>
     <t>type</t>
   </si>
@@ -112,13 +112,13 @@
     <t>minimal</t>
   </si>
   <si>
-    <t>Which of the eight WASA interventions does this site demonstrate?</t>
+    <t>Which of the eight WASA interventions does this site demonstrate? Pick 'Other' if it does not match any.</t>
   </si>
   <si>
     <t>Type / sub-category</t>
   </si>
   <si>
-    <t>Free-text sub-type, e.g. live fencing, cover crop, stone bund, farm pond</t>
+    <t>Free-text sub-type. If intervention is 'Other', describe the intervention here.</t>
   </si>
   <si>
     <t>description</t>
@@ -274,6 +274,12 @@
     <t>H - Climate Information Services</t>
   </si>
   <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Other (describe in the Type field)</t>
+  </si>
+  <si>
     <t>form_title</t>
   </si>
   <si>
@@ -295,7 +301,7 @@
     <t>wasa_intervention_v2</t>
   </si>
   <si>
-    <t>2026.05.28.2</t>
+    <t>2026.05.28.3</t>
   </si>
   <si>
     <t>en</t>
@@ -661,7 +667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63D1AEA8-E490-4A79-BF69-B3584A8A2767}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7529D4A-3BB1-4C82-AE2F-91C2ADAB0825}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -670,7 +676,7 @@
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="95.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -957,8 +963,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFBD1968-0C81-4C75-9DCC-6B68690BADFF}">
-  <dimension ref="A1:C9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4E0FA6-FEF3-4B63-86A4-FC693BACCEBC}">
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
@@ -1065,13 +1071,24 @@
         <v>76</v>
       </c>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5023EBA-5FD9-4A94-92A1-EE79071BBC46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF59FE5-BE51-4AFB-A16D-E1B3F44150AA}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1084,36 +1101,36 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>

--- a/wasa-intervention-form.xlsx
+++ b/wasa-intervention-form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F16ED20-C14F-485A-A608-C3705299E172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E3B467E-AB94-46FE-83B1-DE7314698FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24EAA487-CC81-403E-BAAF-7584F6353F78}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{98AECFF5-080F-4D6C-9661-4A32B6F2F451}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="91">
   <si>
     <t>type</t>
   </si>
@@ -85,6 +85,19 @@
     <t>device_id</t>
   </si>
   <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>intro_note</t>
+  </si>
+  <si>
+    <t>## Record a WASA intervention site_x000D_
+_x000D_
+Capture a WASA intervention as you visit it. Select the intervention type, write a short description, capture GPS, and take **at least 3 geotagged photos**. Required fields are marked with *._x000D_
+_x000D_
+**Before you start:** make sure device location services are ON so each photo carries an EXIF GPS tag.</t>
+  </si>
+  <si>
     <t>text</t>
   </si>
   <si>
@@ -148,9 +161,6 @@
     <t>Capture the GPS coordinates of this site</t>
   </si>
   <si>
-    <t>note</t>
-  </si>
-  <si>
     <t>photos_note</t>
   </si>
   <si>
@@ -301,7 +311,7 @@
     <t>wasa_intervention_v2</t>
   </si>
   <si>
-    <t>2026.05.28.3</t>
+    <t>2026.05.28.4</t>
   </si>
   <si>
     <t>en</t>
@@ -351,8 +361,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -667,8 +680,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7529D4A-3BB1-4C82-AE2F-91C2ADAB0825}">
-  <dimension ref="A1:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0762B124-EEA5-4F3D-9528-5D400BE593EA}">
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -680,26 +693,26 @@
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -735,226 +748,237 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
         <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C9" t="s">
         <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" t="s">
         <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
         <v>30</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>37</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
         <v>39</v>
       </c>
-      <c r="B12" t="s">
+      <c r="F12" t="s">
         <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" t="s">
         <v>44</v>
       </c>
-      <c r="C13" t="s">
+      <c r="G13" t="s">
         <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
         <v>50</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
         <v>51</v>
       </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
       </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
         <v>54</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>55</v>
       </c>
-      <c r="G16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>56</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" t="s">
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
         <v>58</v>
       </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="C18" t="s">
         <v>59</v>
+      </c>
+      <c r="D18" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -963,7 +987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B4E0FA6-FEF3-4B63-86A4-FC693BACCEBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722D1BBA-FD46-4A8E-8591-4592597C06D8}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -972,114 +996,114 @@
     <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1112,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF59FE5-BE51-4AFB-A16D-E1B3F44150AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5059094-DD49-403C-8E66-119B09CCCF2D}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1099,38 +1123,38 @@
     <col min="5" max="5" width="71.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>83</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/wasa-intervention-form.xlsx
+++ b/wasa-intervention-form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E3B467E-AB94-46FE-83B1-DE7314698FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F96BBA2-3BEE-4D8A-8465-740DB484EF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{98AECFF5-080F-4D6C-9661-4A32B6F2F451}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0E82CBD0-98DB-45A7-8BFF-FD603CF9C37C}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -91,10 +91,8 @@
     <t>intro_note</t>
   </si>
   <si>
-    <t>## Record a WASA intervention site_x000D_
-_x000D_
-Capture a WASA intervention as you visit it. Select the intervention type, write a short description, capture GPS, and take **at least 3 geotagged photos**. Required fields are marked with *._x000D_
-_x000D_
+    <t>## Record a WASA intervention site
+Capture a WASA intervention as you visit it. Select the intervention type, write a short description, capture GPS, and take **at least 3 geotagged photos**. Required fields are marked with *.
 **Before you start:** make sure device location services are ON so each photo carries an EXIF GPS tag.</t>
   </si>
   <si>
@@ -311,7 +309,7 @@
     <t>wasa_intervention_v2</t>
   </si>
   <si>
-    <t>2026.05.28.4</t>
+    <t>2026.05.28.5</t>
   </si>
   <si>
     <t>en</t>
@@ -680,7 +678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0762B124-EEA5-4F3D-9528-5D400BE593EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6840E34-3AC2-4119-B785-3C48BDD58FB9}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -987,7 +985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722D1BBA-FD46-4A8E-8591-4592597C06D8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8922A8-A0B9-4C55-9E89-617ABE298078}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1112,7 +1110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5059094-DD49-403C-8E66-119B09CCCF2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF4AA86-EE8C-4C0B-9E3D-F26E1BFD3493}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/wasa-intervention-form.xlsx
+++ b/wasa-intervention-form.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\z.kiala\Documents\water_cycle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F96BBA2-3BEE-4D8A-8465-740DB484EF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3AF5415C-8C6D-4835-ADC4-13C600546398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{0E82CBD0-98DB-45A7-8BFF-FD603CF9C37C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E5D8A89E-677F-4FD0-B97C-11604E60329B}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -129,7 +129,7 @@
     <t>Type / sub-category</t>
   </si>
   <si>
-    <t>Free-text sub-type. If intervention is 'Other', describe the intervention here.</t>
+    <t>Examples: Replants tree cover, Minimum tillage, Mulching, Contour bunds, Mulch strips, Grass tufts, Tied ridges, Soil ripping, Farm pond, Check dam, Cover crop, Live fencing. If intervention is 'Other', describe the intervention here.</t>
   </si>
   <si>
     <t>description</t>
@@ -309,7 +309,7 @@
     <t>wasa_intervention_v2</t>
   </si>
   <si>
-    <t>2026.05.28.5</t>
+    <t>2026.05.28.6</t>
   </si>
   <si>
     <t>en</t>
@@ -678,7 +678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6840E34-3AC2-4119-B785-3C48BDD58FB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{474155D3-969C-411B-BB4D-3D65C4139C40}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -687,7 +687,7 @@
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="95.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="210.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -985,7 +985,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE8922A8-A0B9-4C55-9E89-617ABE298078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E50C1FEB-0B2F-47D3-B7CD-7F6FFC31FFCD}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1110,7 +1110,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEF4AA86-EE8C-4C0B-9E3D-F26E1BFD3493}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0720FEC6-9990-4700-BC70-388C8BA43CA1}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
